--- a/public/mau-nhap-danh-sach-hang-hoa-pr.xlsx
+++ b/public/mau-nhap-danh-sach-hang-hoa-pr.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Danh sách hàng hóa" sheetId="1" r:id="Ra2de5e9ea7944b3e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Danh sách hàng hóa" sheetId="1" r:id="R47f653e29edf414c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -563,102 +563,45 @@
       </x:c>
     </x:row>
     <x:row r="5" ht="23" customHeight="1">
-      <x:c r="A5" s="23" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B5" s="15" t="str">
-        <x:v>VT-001</x:v>
-      </x:c>
-      <x:c r="C5" s="15" t="str">
-        <x:v>Cơ khí</x:v>
-      </x:c>
-      <x:c r="D5" s="15" t="str">
-        <x:v>Vòng bi SKF 6205-2RS</x:v>
-      </x:c>
-      <x:c r="E5" s="15" t="str">
-        <x:v>Thép không gỉ, chịu tải cao</x:v>
-      </x:c>
-      <x:c r="F5" s="15" t="str">
-        <x:v>25×52×15 mm</x:v>
-      </x:c>
-      <x:c r="G5" s="26" t="str">
-        <x:v>Cái</x:v>
-      </x:c>
-      <x:c r="H5" s="29" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="I5" s="38" t="n">
-        <x:v>85000</x:v>
-      </x:c>
-      <x:c r="J5" s="39" t="n">
+      <x:c r="A5" s="23"/>
+      <x:c r="B5" s="15"/>
+      <x:c r="C5" s="15"/>
+      <x:c r="D5" s="15"/>
+      <x:c r="E5" s="15"/>
+      <x:c r="F5" s="15"/>
+      <x:c r="G5" s="26"/>
+      <x:c r="H5" s="29"/>
+      <x:c r="I5" s="38"/>
+      <x:c r="J5" s="39" t="str">
         <x:f>IF(OR(H5="",I5=""),"",H5*I5)</x:f>
-        <x:v>1700000</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="23" customHeight="1">
-      <x:c r="A6" s="24" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B6" s="18" t="str">
-        <x:v>VT-002</x:v>
-      </x:c>
-      <x:c r="C6" s="18" t="str">
-        <x:v>Truyền động</x:v>
-      </x:c>
-      <x:c r="D6" s="18" t="str">
-        <x:v>Dây curoa B-68</x:v>
-      </x:c>
-      <x:c r="E6" s="18" t="str">
-        <x:v>Cao su chịu mài mòn</x:v>
-      </x:c>
-      <x:c r="F6" s="18" t="str">
-        <x:v>B-68</x:v>
-      </x:c>
-      <x:c r="G6" s="27" t="str">
-        <x:v>Cái</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I6" s="40" t="n">
-        <x:v>95000</x:v>
-      </x:c>
-      <x:c r="J6" s="41" t="n">
+      <x:c r="A6" s="24"/>
+      <x:c r="B6" s="18"/>
+      <x:c r="C6" s="18"/>
+      <x:c r="D6" s="18"/>
+      <x:c r="E6" s="18"/>
+      <x:c r="F6" s="18"/>
+      <x:c r="G6" s="27"/>
+      <x:c r="H6" s="32"/>
+      <x:c r="I6" s="40"/>
+      <x:c r="J6" s="41" t="str">
         <x:f>IF(OR(H6="",I6=""),"",H6*I6)</x:f>
-        <x:v>1425000</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="23" customHeight="1">
-      <x:c r="A7" s="24" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B7" s="18" t="str">
-        <x:v>VT-003</x:v>
-      </x:c>
-      <x:c r="C7" s="18" t="str">
-        <x:v>Van &amp; phụ kiện</x:v>
-      </x:c>
-      <x:c r="D7" s="18" t="str">
-        <x:v>Van bi inox DN25</x:v>
-      </x:c>
-      <x:c r="E7" s="18" t="str">
-        <x:v>Inox 304, ren trong</x:v>
-      </x:c>
-      <x:c r="F7" s="18" t="str">
-        <x:v>DN25</x:v>
-      </x:c>
-      <x:c r="G7" s="27" t="str">
-        <x:v>Cái</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I7" s="40" t="n">
-        <x:v>210000</x:v>
-      </x:c>
-      <x:c r="J7" s="41" t="n">
+      <x:c r="A7" s="24"/>
+      <x:c r="B7" s="18"/>
+      <x:c r="C7" s="18"/>
+      <x:c r="D7" s="18"/>
+      <x:c r="E7" s="18"/>
+      <x:c r="F7" s="18"/>
+      <x:c r="G7" s="27"/>
+      <x:c r="H7" s="32"/>
+      <x:c r="I7" s="40"/>
+      <x:c r="J7" s="41" t="str">
         <x:f>IF(OR(H7="",I7=""),"",H7*I7)</x:f>
-        <x:v>2100000</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="23" customHeight="1">
@@ -2031,7 +1974,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R16859c3b0c1b40b0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra57fdfb1525d4b0c"/>
   </x:tableParts>
 </x:worksheet>
 </file>